--- a/IMRADS/TALISAY/Datasets/Talisay work data.xlsx
+++ b/IMRADS/TALISAY/Datasets/Talisay work data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\Talisay Simulation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\IMRADS\TALISAY\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B383C2E-F4FD-486A-8D55-C650A627A096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0639404-C15C-4525-9888-395C333A52D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Name</t>
   </si>
@@ -44,11 +44,17 @@
   <si>
     <t>Workplace</t>
   </si>
+  <si>
+    <t>14.1229439319374</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000000000000"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -93,7 +99,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,11 +107,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -114,6 +135,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,11 +361,12 @@
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="16" customWidth="1"/>
     <col min="8" max="10" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -372,15 +397,15 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>14.131619061089699</v>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
       </c>
-      <c r="C2">
-        <v>121.132345580346</v>
+      <c r="C2" s="4">
+        <v>121.12766711389099</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="13.2" x14ac:dyDescent="0.25"/>
